--- a/artfynd/A 26261-2026 artfynd.xlsx
+++ b/artfynd/A 26261-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114695013</v>
+        <v>114693662</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>861110</v>
+        <v>861105</v>
       </c>
       <c r="R2" t="n">
-        <v>7499202</v>
+        <v>7499178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
+          <t>2019-05-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
+          <t>2019-05-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +768,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Ulf Sperens</t>
+          <t>Anna Sundelin</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -779,44 +779,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulf Sperens</t>
+          <t>Anna Sundelin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114693662</v>
+        <v>114694698</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,16 +819,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>runt Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861105</v>
+        <v>861135</v>
       </c>
       <c r="R3" t="n">
-        <v>7499178</v>
+        <v>7499258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>hona+6 ägg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,11 +882,7 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Anna Sundelin</t>
-        </is>
-      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -895,44 +891,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Sundelin</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114694698</v>
+        <v>114694856</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102117</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jorduggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asio flammeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,21 +931,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>runt Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861135</v>
+        <v>861110</v>
       </c>
       <c r="R4" t="n">
-        <v>7499258</v>
+        <v>7499202</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,17 +967,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2019-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2019-06-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>hona+6 ägg</t>
+          <t>1ad+1k</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +989,11 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1012,22 +1002,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Ulf Sperens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114694856</v>
+        <v>101096102</v>
       </c>
       <c r="B5" t="n">
-        <v>57221</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,38 +1020,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102117</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jorduggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asio flammeus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>runt Kaunisvaara, Nb</t>
+          <t>Tapulivuoma, barrskog N Patojoki, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861110</v>
+        <v>861120</v>
       </c>
       <c r="R5" t="n">
-        <v>7499202</v>
+        <v>7499290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,17 +1090,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
+          <t>2019-04-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1ad+1k</t>
+          <t>2019-04-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,21 +1116,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Ulf Sperens</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulf Sperens</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1138,12 +1135,7 @@
         <v>114735559</v>
       </c>
       <c r="B6" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,6 +1250,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114695013</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>runt Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>861110</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7499202</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-06-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-06-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26261-2026 artfynd.xlsx
+++ b/artfynd/A 26261-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114694698</v>
+        <v>134752486</v>
       </c>
       <c r="B3" t="n">
-        <v>57141</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,43 +797,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>runt Kaunisvaara, Nb</t>
+          <t>Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861135</v>
+        <v>861145</v>
       </c>
       <c r="R3" t="n">
-        <v>7499258</v>
+        <v>7499256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hona+6 ägg</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +873,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -898,32 +888,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114694856</v>
+        <v>114694698</v>
       </c>
       <c r="B4" t="n">
-        <v>57800</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102117</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jorduggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asio flammeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,16 +921,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>runt Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861110</v>
+        <v>861135</v>
       </c>
       <c r="R4" t="n">
-        <v>7499202</v>
+        <v>7499258</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,17 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1ad+1k</t>
+          <t>hona+6 ägg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,11 +984,7 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Ulf Sperens</t>
-        </is>
-      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1002,68 +993,56 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulf Sperens</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101096102</v>
+        <v>114694856</v>
       </c>
       <c r="B5" t="n">
-        <v>57144</v>
+        <v>57800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>102117</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Jorduggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Asio flammeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tapulivuoma, barrskog N Patojoki, Nb</t>
+          <t>runt Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861120</v>
+        <v>861110</v>
       </c>
       <c r="R5" t="n">
-        <v>7499290</v>
+        <v>7499202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,22 +1069,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2019-06-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2019-06-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1ad+1k</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,26 +1090,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Olsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Olsson</t>
+          <t>Ulf Sperens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114735559</v>
+        <v>134751675</v>
       </c>
       <c r="B6" t="n">
-        <v>57144</v>
+        <v>57153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,16 +1122,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,12 +1141,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1177,14 +1151,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861123</v>
+        <v>861182</v>
       </c>
       <c r="R6" t="n">
-        <v>7499291</v>
+        <v>7498914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,17 +1185,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spel, 2-3 tuppar</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,11 +1211,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1246,17 +1220,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Olsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114695013</v>
+        <v>134751678</v>
       </c>
       <c r="B7" t="n">
-        <v>58636</v>
+        <v>57153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,16 +1238,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1286,16 +1260,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>runt Kaunisvaara, Nb</t>
+          <t>Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861110</v>
+        <v>861166</v>
       </c>
       <c r="R7" t="n">
-        <v>7499202</v>
+        <v>7499032</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1301,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,11 +1327,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Ulf Sperens</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1336,360 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>101096102</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tapulivuoma, barrskog N Patojoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>861120</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7499290</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-04-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-04-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114735559</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>861123</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7499291</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-04-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-04-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>spel, 2-3 tuppar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114695013</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>runt Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>861110</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7499202</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-06-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-06-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>Ulf Sperens</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulf Sperens</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26261-2026 artfynd.xlsx
+++ b/artfynd/A 26261-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114693662</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752486</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114694698</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114694856</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134751675</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134751678</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101096102</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114735559</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1690,8 +1735,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114695013</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>